--- a/test.xlsx
+++ b/test.xlsx
@@ -1,109 +1,208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <s:workbookPr/>
-  <s:bookViews>
-    <s:workbookView xWindow="3160" yWindow="2260" windowWidth="28240" windowHeight="17240"/>
-  </s:bookViews>
-  <s:sheets>
-    <s:sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
-  </s:sheets>
-  <s:calcPr calcId="181029"/>
-</s:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
+  </sheets>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:si>
-    <s:t>ИНН</s:t>
-  </s:si>
-</s:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t xml:space="preserve">ИНН</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<s:styleSheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:numFmts count="0"/>
-  <s:fonts count="6">
-    <s:font>
-      <s:name val="Arial"/>
-      <s:family val="2"/>
-      <s:color theme="1"/>
-      <s:sz val="10"/>
-    </s:font>
-    <s:font>
-      <s:name val="Segoe UI"/>
-      <s:b val="1"/>
-      <s:color rgb="FF0F1115"/>
-    </s:font>
-    <s:font>
-      <s:name val="Arial"/>
-      <s:family val="2"/>
-      <s:b val="1"/>
-      <s:color theme="1"/>
-      <s:sz val="10"/>
-    </s:font>
-    <s:font>
-      <s:name val="Arial"/>
-      <s:b val="1"/>
-      <s:color rgb="FF0F1115"/>
-    </s:font>
-    <s:font>
-      <s:name val="Arial"/>
-      <s:family val="2"/>
-      <s:b val="0"/>
-      <s:color theme="1"/>
-      <s:sz val="10"/>
-    </s:font>
-    <s:font>
-      <s:name val="Arial"/>
-      <s:b val="0"/>
-      <s:color rgb="FF0F1115"/>
-    </s:font>
-  </s:fonts>
-  <s:fills count="2">
-    <s:fill>
-      <s:patternFill patternType="none"/>
-    </s:fill>
-    <s:fill>
-      <s:patternFill patternType="gray125"/>
-    </s:fill>
-  </s:fills>
-  <s:borders count="1">
-    <s:border>
-      <s:left/>
-      <s:right/>
-      <s:top/>
-      <s:bottom/>
-      <s:diagonal/>
-    </s:border>
-  </s:borders>
-  <s:cellStyleXfs count="1">
-    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </s:cellStyleXfs>
-  <s:cellXfs count="6">
-    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <s:xf fontId="1" applyFont="1"/>
-    <s:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <s:xf fontId="3" applyFont="1"/>
-    <s:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <s:xf fontId="5" applyFont="1"/>
-  </s:cellXfs>
-  <s:cellStyles count="1">
-    <s:cellStyle name="Обычный" xfId="0" builtinId="0" customBuiltin="1"/>
-  </s:cellStyles>
-  <s:dxfs count="0"/>
-</s:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF0F1115"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -138,61 +237,55 @@
     </a:clrScheme>
     <a:fontScheme name="Arial">
       <a:majorFont>
-        <a:latin typeface="Arial" panose="020B0604020202020204"/>
+        <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" panose="020B0604020202020204"/>
+        <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -200,33 +293,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -239,13 +323,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -255,15 +333,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -271,7 +347,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -279,11 +354,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -292,20 +367,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:dimension ref="A1"/>
-  <s:sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
-  <s:sheetData>
-    <s:row r="1">
-      <s:c r="A1" s="4" t="s">
-        <s:v>0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="2">
-      <s:c r="A2" s="5">
-        <s:v>231138771115</s:v>
-      </s:c>
-    </s:row>
-  </s:sheetData>
-</s:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="13.3984375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
+        <v>231138771115</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
+        <v>123456789012</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>123234556</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>